--- a/دعاوى-متأخرات-ومخالفات.xlsx
+++ b/دعاوى-متأخرات-ومخالفات.xlsx
@@ -30449,7 +30449,7 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>أيمن خليفة حمادي</t>
+          <t>ايمن خليفة حمادي</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -49021,7 +49021,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>أيمن خليفة حمادي</t>
+          <t>ايمن خليفة حمادي</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
